--- a/human_validation/judge/kor/judge_D020_S004_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D020_S004_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,418 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 누나랑 조카가 다시 집에 들어온 뒤로 제가 훨씬 더 예민해지고 좀 처지는 느낌이 들어서 왔어요. 집에서 사소한 일에도 계속 날카롭게 굴게 되고, 그러고는 이미 지친 상태로 수업이나 정비소에 가요. 그럭저럭 버티고는 있는데, 마감을 몇 번 놓쳤고 연극 무대 작업 돕는 것도 그만뒀어요, 모든 걸 제대로 챙길 수가 없었거든요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 요즘 불안하다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네, 그래요. 누나랑 조카가 다시 집에 들어온 뒤로 평소보다 더 예민해진 느낌이에요. 집에서 사소한 일에도 확 반응하게 되고, 그러고는 이미 지친 상태로 수업이나 정비소에 가요. 그럭저럭 관리는 하고 있는데, 모든 걸 제대로 챙기기가 더 힘들어졌어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 살고 싶지 않다거나 차라리 죽었으면 하는 생각이 드신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 아니요, 그런 생각은 안 했어요. 벅차고 스트레스받긴 하는데, 죽고 싶다거나 그런 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 공황발작을 겪은 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 그런 것 같지는 않아요. 정말 스트레스받고 긴장되긴 했는데, 공황발작이라고 부를 만한 건 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 계속 반복하고 싶다는 충동이 드는 생각이나 행동이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 아니요, 그런 건 딱히 못 느꼈어요. 스트레스는 받는데, 특정 생각이나 행동을 계속 반복해야 한다는 느낌은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 평소 좋아하시던 일들을 즐기고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 솔직히 예전만큼은 아니에요. 여전히 하루하루 뭔가를 하고는 있는데, 누나랑 조카가 다시 들어온 뒤로 더 예민해지고 좀 처지는 느낌이에요. 너무 지쳐서 평소처럼 수업이랑 정비소 일을 따라가지 못했고, 마감을 몇 번 놓쳤고, 연극 무대 작업 돕는 것도 그만뒀어요, 모든 걸 제대로 챙길 수가 없었거든요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 이런 느낌이 든 지는 얼마나 되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 이제 한 달 정도 됐어요, 거의 누나랑 조카가 다시 집에 들어온 때부터요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 예전에는 즐기셨지만 지금은 더 이상 즐거움을 느끼지 못하는 일들이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네, 어느 정도는요. 예전에는 연극 무대 작업을 돕고 수업이랑 정비소 일을 잘 챙기는 걸 즐겼는데, 요즘은 그만큼의 흥미나 기운이 없어요. 누나랑 조카가 다시 집에 들어온 뒤로 더 예민해지고 처지는 느낌이고, 결국 모든 걸 제대로 챙길 수 없어서 연극 일도 그만두게 됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 식욕이나 수면 패턴에 변화가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 먹는 거나 자는 거에 큰 변화는 딱히 못 느꼈어요. 가끔 좀 이상한 느낌이 들 때도 있긴 한데, 딱히 눈에 띄는 건 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 지금 느끼시는 상태 때문에 특정 사람, 장소, 활동을 피하고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 네, 조금은 그런 것 같아요. 여전히 수업이랑 일은 나가고 있는데, 지역 극단 무대 프로젝트는 모든 걸 따라갈 수가 없어서 그만둬야 했어요. 그리고 과제도 몇 개 늦게 냈는데, 저답지 않은 일이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 사람들과의 교류를 피하거나 친구들과 보내는 시간이 줄었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 잘 모르겠어요. 일부러 친구들을 피하고 있는 것 같지는 않아요. 그냥 좀 바쁘고 정신이 없어서 예전만큼 먼저 연락을 안 하고 있는 것 같긴 한데, 딱히 크게 느낀 건 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 체중에 큰 변화가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 아니요, 체중에 큰 변화는 못 느꼈어요. 옷도 예전이랑 비슷하게 맞아서, 아닌 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 자신이 쓸모없다거나 죄책감이 든다고 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 딱히 없어요. 그러니까, 가끔 이것저것 스트레스받긴 하는데, 제가 쓸모없다거나 특별히 죄책감을 느낀다고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 하루 대부분 슬프거나 기분이 처진다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 네, 그들이 다시 들어온 뒤로 평소보다 더 처지는 느낌이에요. 매일 하루 종일 끊임없이 그런 건 아니지만, 확실히 더 예민하고 지쳐 있어요. 이미 지친 상태로 수업이나 정비소에 가고, 그것 때문에 이것저것 따라가기가 더 힘들어졌어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 이 스트레스와 처지는 느낌이 누나와 조카분이 다시 집에 들어온 것과 직접적으로 관련이 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 네, 직접적으로 관련이 있다고 생각해요. 정말 누나랑 조카가 다시 집에 들어온 뒤부터 시작됐어요. 그 이후로 더 예민하고 처지는 느낌이고, 집에서 사소한 일에도 날카롭게 굴어요. 그러고는 이미 지친 상태로 수업이나 정비소에 가고요. 그럭저럭 관리는 하고 있는데, 마감을 몇 번 놓쳤고 모든 걸 제대로 챙길 수가 없어서 연극 무대 작업 돕는 것도 그만뒀어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 요즘 여러 가지 다양한 일에 대해 걱정하고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 여러 가지 다양한 거라고까지는 말 못 하겠어요. 대부분 집안일이랑 학교, 일을 따라가려는 것에 관한 거예요. 이것저것 전반적으로 다 걱정하고 있다는 느낌은 딱히 못 받았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 요즘 불쾌하거나 불쑥 떠오르는 생각들이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 아니요, 딱히 없어요. 그러니까, 스트레스받고 짜증 나긴 하는데, 불쾌하게 느껴지거나 불쑥 떠올라서 떨쳐낼 수 없는 그런 생각들은 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 만약 누나와 조카분이 더 이상 함께 살지 않는 것처럼 생활 환경이 바뀐다면, 예민하고 처지는 느낌이 나아질 거라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 네, 아마 나아질 거라고 생각해요. 그러니까, 상황이 아직 딱히 바뀌지 않았거든요, 누나랑 조카는 여전히 저희랑 같이 살고 있어서, 여전히 집안의 그 같은 문제랑 연결되어 있는 것 같아요. 만약 그게 바뀐다면, 덜 예민해질 거라고 생각해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 집을 떠나 계시거나 누나와 조카분을 직접 상대하지 않을 때, 증상이 크게 줄어드는 걸 경험하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 네, 어느 정도는요. 수업이나 정비소처럼 집을 떠나 있을 때는 그들을 직접 상대하지 않아서 조금 더 수월할 수 있어요. 근데 보통 이미 집안일 때문에 지쳐 있는 상태라, 여전히 영향을 받아요. 그럭저럭 버티고는 있는데, 마감을 몇 번 놓쳤고 모든 걸 제대로 챙길 수 없어서 연극 무대 작업 돕는 것도 그만뒀어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>진단명: 적응장애 (D020)
 인구통계: 성별 남성 / 나이 18 / 직업상태 industrial or refractory machinery mechanic / 최종학력 대학 재학
@@ -575,467 +978,29 @@
 증상 지속 기간: 1 month
 추가 요건: Symptoms must develop within 3 months of the onset of the stressor, Within 6 months of the termination of the stressor or its consequences
 주호소 증상 코드: S081
-배경 서술: 니콜라스 폴리의 누나가 힘든 이별을 겪은 뒤 갓난아기와 함께 다시 본가로 들어오면서, 안 그래도 바빴던 그의 집은 붐비고 예측할 수 없는 공간이 되어버렸다. 하필 그는 정비 훈련과 시간제 정비소 근무, 대학 과제를 병행하고 있던 시기였다. 그 후 한 달 동안 예산 관리, 기타 연습, 메이커 프로젝트, 픽업 농구를 꾸준히 이어가던 평소의 패턴이 더 유지하기 힘들어졌는데, 새로운 가족의 요구에 대한 그의 반응이 계속 학교와 직장으로까지 번졌기 때문이었다. 지장은 눈에 띄었지만 제한적이었다. 그는 여전히 자기 할 일에 임하고 있었지만, 마감을 놓쳤고 열의를 갖고 참여하던 지역 극단 무대 제작 프로젝트에서는 발을 뺐다. 그는 정기 학사 지도 상담 중에 스스로 이 문제를 꺼냈고, 지도교수는 학생 상담 서비스를 통해 평가를 예약할 수 있도록 도와주었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 누나랑 조카가 다시 집에 들어온 뒤로 제가 훨씬 더 예민해지고 좀 처지는 느낌이 들어서 왔어요. 집에서 사소한 일에도 계속 날카롭게 굴게 되고, 그러고는 이미 지친 상태로 수업이나 정비소에 가요. 그럭저럭 버티고는 있는데, 마감을 몇 번 놓쳤고 연극 무대 작업 돕는 것도 그만뒀어요, 모든 걸 제대로 챙길 수가 없었거든요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 요즘 불안하다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네, 그래요. 누나랑 조카가 다시 집에 들어온 뒤로 평소보다 더 예민해진 느낌이에요. 집에서 사소한 일에도 확 반응하게 되고, 그러고는 이미 지친 상태로 수업이나 정비소에 가요. 그럭저럭 관리는 하고 있는데, 모든 걸 제대로 챙기기가 더 힘들어졌어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 살고 싶지 않다거나 차라리 죽었으면 하는 생각이 드신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 아니요, 그런 생각은 안 했어요. 벅차고 스트레스받긴 하는데, 죽고 싶다거나 그런 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 공황발작을 겪은 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 그런 것 같지는 않아요. 정말 스트레스받고 긴장되긴 했는데, 공황발작이라고 부를 만한 건 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 계속 반복하고 싶다는 충동이 드는 생각이나 행동이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 아니요, 그런 건 딱히 못 느꼈어요. 스트레스는 받는데, 특정 생각이나 행동을 계속 반복해야 한다는 느낌은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 평소 좋아하시던 일들을 즐기고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 솔직히 예전만큼은 아니에요. 여전히 하루하루 뭔가를 하고는 있는데, 누나랑 조카가 다시 들어온 뒤로 더 예민해지고 좀 처지는 느낌이에요. 너무 지쳐서 평소처럼 수업이랑 정비소 일을 따라가지 못했고, 마감을 몇 번 놓쳤고, 연극 무대 작업 돕는 것도 그만뒀어요, 모든 걸 제대로 챙길 수가 없었거든요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 이런 느낌이 든 지는 얼마나 되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 이제 한 달 정도 됐어요, 거의 누나랑 조카가 다시 집에 들어온 때부터요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 예전에는 즐기셨지만 지금은 더 이상 즐거움을 느끼지 못하는 일들이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네, 어느 정도는요. 예전에는 연극 무대 작업을 돕고 수업이랑 정비소 일을 잘 챙기는 걸 즐겼는데, 요즘은 그만큼의 흥미나 기운이 없어요. 누나랑 조카가 다시 집에 들어온 뒤로 더 예민해지고 처지는 느낌이고, 결국 모든 걸 제대로 챙길 수 없어서 연극 일도 그만두게 됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 식욕이나 수면 패턴에 변화가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 먹는 거나 자는 거에 큰 변화는 딱히 못 느꼈어요. 가끔 좀 이상한 느낌이 들 때도 있긴 한데, 딱히 눈에 띄는 건 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 지금 느끼시는 상태 때문에 특정 사람, 장소, 활동을 피하고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 네, 조금은 그런 것 같아요. 여전히 수업이랑 일은 나가고 있는데, 지역 극단 무대 프로젝트는 모든 걸 따라갈 수가 없어서 그만둬야 했어요. 그리고 과제도 몇 개 늦게 냈는데, 저답지 않은 일이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 사람들과의 교류를 피하거나 친구들과 보내는 시간이 줄었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 잘 모르겠어요. 일부러 친구들을 피하고 있는 것 같지는 않아요. 그냥 좀 바쁘고 정신이 없어서 예전만큼 먼저 연락을 안 하고 있는 것 같긴 한데, 딱히 크게 느낀 건 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 지속성 우울장애 (D014); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 체중에 큰 변화가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 아니요, 체중에 큰 변화는 못 느꼈어요. 옷도 예전이랑 비슷하게 맞아서, 아닌 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 자신이 쓸모없다거나 죄책감이 든다고 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 딱히 없어요. 그러니까, 가끔 이것저것 스트레스받긴 하는데, 제가 쓸모없다거나 특별히 죄책감을 느낀다고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 누나와 조카분이 다시 집에 들어온 이후로 하루 대부분 슬프거나 기분이 처진다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 네, 그들이 다시 들어온 뒤로 평소보다 더 처지는 느낌이에요. 매일 하루 종일 끊임없이 그런 건 아니지만, 확실히 더 예민하고 지쳐 있어요. 이미 지친 상태로 수업이나 정비소에 가고, 그것 때문에 이것저것 따라가기가 더 힘들어졌어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 이 스트레스와 처지는 느낌이 누나와 조카분이 다시 집에 들어온 것과 직접적으로 관련이 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 네, 직접적으로 관련이 있다고 생각해요. 정말 누나랑 조카가 다시 집에 들어온 뒤부터 시작됐어요. 그 이후로 더 예민하고 처지는 느낌이고, 집에서 사소한 일에도 날카롭게 굴어요. 그러고는 이미 지친 상태로 수업이나 정비소에 가고요. 그럭저럭 관리는 하고 있는데, 마감을 몇 번 놓쳤고 모든 걸 제대로 챙길 수가 없어서 연극 무대 작업 돕는 것도 그만뒀어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 요즘 여러 가지 다양한 일에 대해 걱정하고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 여러 가지 다양한 거라고까지는 말 못 하겠어요. 대부분 집안일이랑 학교, 일을 따라가려는 것에 관한 거예요. 이것저것 전반적으로 다 걱정하고 있다는 느낌은 딱히 못 받았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 요즘 불쾌하거나 불쑥 떠오르는 생각들이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 아니요, 딱히 없어요. 그러니까, 스트레스받고 짜증 나긴 하는데, 불쾌하게 느껴지거나 불쑥 떠올라서 떨쳐낼 수 없는 그런 생각들은 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 만약 누나와 조카분이 더 이상 함께 살지 않는 것처럼 생활 환경이 바뀐다면, 예민하고 처지는 느낌이 나아질 거라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 네, 아마 나아질 거라고 생각해요. 그러니까, 상황이 아직 딱히 바뀌지 않았거든요, 누나랑 조카는 여전히 저희랑 같이 살고 있어서, 여전히 집안의 그 같은 문제랑 연결되어 있는 것 같아요. 만약 그게 바뀐다면, 덜 예민해질 거라고 생각해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 집을 떠나 계시거나 누나와 조카분을 직접 상대하지 않을 때, 증상이 크게 줄어드는 걸 경험하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 네, 어느 정도는요. 수업이나 정비소처럼 집을 떠나 있을 때는 그들을 직접 상대하지 않아서 조금 더 수월할 수 있어요. 근데 보통 이미 집안일 때문에 지쳐 있는 상태라, 여전히 영향을 받아요. 그럭저럭 버티고는 있는데, 마감을 몇 번 놓쳤고 모든 걸 제대로 챙길 수 없어서 연극 무대 작업 돕는 것도 그만뒀어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
+배경 서술: 니콜라스 폴리의 누나가 힘든 이별을 겪은 뒤 갓난아기와 함께 다시 본가로 들어오면서, 안 그래도 바빴던 그의 집은 붐비고 예측할 수 없는 공간이 되어버렸다. 하필 그는 정비 훈련과 시간제 정비소 근무, 대학 과제를 병행하고 있던 시기였다. 그 후 한 달 동안 예산 관리, 기타 연습, 메이커 프로젝트, 픽업 농구를 꾸준히 이어가던 평소의 패턴이 더 유지하기 힘들어졌는데, 새로운 가족의 요구에 대한 그의 반응이 계속 학교와 직장으로까지 번졌기 때문이었다. 지장은 눈에 띄었지만 제한적이었다. 그는 여전히 자기 할 일에 임하고 있었지만, 마감을 놓쳤고 열의를 갖고 참여하던 지역 극단 무대 제작 프로젝트에서는 발을 뺐다. 그는 정기 학사 지도 상담 중에 스스로 이 문제를 꺼냈고, 지도교수는 학생 상담 서비스를 통해 평가를 예약할 수 있도록 도와주었다.
+표집된 증상 목록:
+  - S081 스트레스 관련 부적응 반응: 확인 가능한 스트레스 요인에 대한 반응으로 나타나는 정서적·행동적 증상.</t>
+        </is>
+      </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: adjustment_symptoms (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 스트레스 관련 부적응 반응: 확인 가능한 스트레스 요인에 대한 반응으로 나타나는 정서적·행동적 증상.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.0)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 0.5
+체크리스트 그룹: adjustment_symptoms (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 스트레스 관련 부적응 반응: 확인 가능한 스트레스 요인에 대한 반응으로 나타나는 정서적·행동적 증상.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D020_S004_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D020_S004_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -964,6 +964,11 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -996,11 +1001,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D020_S004_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D020_S004_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.177</v>
+        <v>0.3421</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.6404</v>
+        <v>0.3421</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1956</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.3889</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.875</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
